--- a/artfynd/A 52898-2025 artfynd.xlsx
+++ b/artfynd/A 52898-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127652590</v>
+        <v>127652593</v>
       </c>
       <c r="B2" t="n">
-        <v>101739</v>
+        <v>107612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>1897</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -764,6 +764,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>enstaka ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
         <v>127652592</v>
       </c>
       <c r="B3" t="n">
-        <v>101548</v>
+        <v>102225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127652593</v>
+        <v>127652590</v>
       </c>
       <c r="B4" t="n">
-        <v>106866</v>
+        <v>102419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1897</v>
+        <v>221317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,11 +1001,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>enstaka ex</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52898-2025 artfynd.xlsx
+++ b/artfynd/A 52898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127652593</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127652592</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,8 +1040,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127652590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>